--- a/Unity/Assets/Config/Excel/SceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SceneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SceneProto" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -468,10 +468,7 @@
     <t>天空之城</t>
   </si>
   <si>
-    <t>-5709,179,-2662,1500</t>
-  </si>
-  <si>
-    <t>0,0,-500</t>
+    <t>-1733,0,163</t>
   </si>
   <si>
     <t>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010</t>
@@ -1939,17 +1936,15 @@
         <v>61</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="J6" s="8">
         <v>101</v>
@@ -1973,16 +1968,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="S6" s="8">
         <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U6" s="8">
         <v>0</v>
@@ -1997,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="Y6" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z6" s="6"/>
       <c r="AA6" s="6"/>
@@ -2011,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="AE6" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
